--- a/Sajjad data/by_country_and_state/USA/MA.xlsx
+++ b/Sajjad data/by_country_and_state/USA/MA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="390">
   <si>
     <t>Business Name</t>
   </si>
@@ -362,6 +362,825 @@
   </si>
   <si>
     <t>2026-10-25T19:35:27.922Z</t>
+  </si>
+  <si>
+    <t>Dr. Ihab Dabbagh, DMD</t>
+  </si>
+  <si>
+    <t>(508) 595-9432</t>
+  </si>
+  <si>
+    <t>9 Millbrook St, Worcester, MA 01606</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Ihab+Dabbagh,+DMD/data=!4m7!3m6!1s0x89e407abbdc8c80b:0x1a350daf178350f7!8m2!3d42.2905351!4d-71.8056719!16s%2Fg%2F1v_w3chq!19sChIJC8jIvasH5IkR91CDF68NNRo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:22:27.231Z</t>
+  </si>
+  <si>
+    <t>Dr. Robert M. Mccarthy, DMD</t>
+  </si>
+  <si>
+    <t>(508) 756-6325</t>
+  </si>
+  <si>
+    <t>548 Pleasant St #1, Worcester, MA 01602</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Robert+M.+Mccarthy,+DMD/data=!4m7!3m6!1s0x89e4068e2235ca5b:0xe94b3f4fbae2799!8m2!3d42.2642429!4d-71.8211181!16s%2Fg%2F1tlc928j!19sChIJW8o1Io4G5IkRmSeu-_SzlA4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:22:38.191Z</t>
+  </si>
+  <si>
+    <t>Dr. Peter A. Stathoulopoulos, DMD</t>
+  </si>
+  <si>
+    <t>(508) 755-7171</t>
+  </si>
+  <si>
+    <t>251 Salisbury St, Worcester, MA 01609</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Peter+A.+Stathoulopoulos,+DMD/data=!4m7!3m6!1s0x89e406f51b5a46a9:0xbd178daee2f050c8!8m2!3d42.280593!4d-71.8126957!16s%2Fg%2F1w3w4103!19sChIJqUZaG_UG5IkRyFDw4q6NF70?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:22:47.426Z</t>
+  </si>
+  <si>
+    <t>Premier Family Dental Group</t>
+  </si>
+  <si>
+    <t>(508) 853-3394</t>
+  </si>
+  <si>
+    <t>610 W Boylston St, Worcester, MA 01606</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Premier+Family+Dental+Group/data=!4m7!3m6!1s0x89e407627f2c03d1:0x6d8082165f1aa52d!8m2!3d42.3124703!4d-71.7972915!16s%2Fg%2F11rt_ygdhj!19sChIJ0QMsf2IH5IkRLaUaXxaCgG0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:23:04.444Z</t>
+  </si>
+  <si>
+    <t>Dr. Phuong T. Pham, DMD</t>
+  </si>
+  <si>
+    <t>(508) 798-8525</t>
+  </si>
+  <si>
+    <t>17 Daniels St, Worcester, MA 01604</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Phuong+T.+Pham,+DMD/data=!4m7!3m6!1s0x89e4062fdd271a05:0xde5fddd9ba8e15f7!8m2!3d42.2733567!4d-71.7734452!16s%2Fg%2F1tk1n_m8!19sChIJBRon3S8G5IkR9xWOutndX94?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:23:13.212Z</t>
+  </si>
+  <si>
+    <t>Vera Chengeto DDS</t>
+  </si>
+  <si>
+    <t>(508) 754-9825</t>
+  </si>
+  <si>
+    <t>144 Pleasant St, Worcester, MA 01609</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Vera+Chengeto+DDS/data=!4m7!3m6!1s0x89e40661841e213d:0xdd7f8cc108a327ed!8m2!3d42.2635665!4d-71.8071982!16s%2Fg%2F1tcx2j_v!19sChIJPSEehGEG5IkR7SejCMGMf90?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:23:48.329Z</t>
+  </si>
+  <si>
+    <t>Dr. Gregory Livanos, DDS</t>
+  </si>
+  <si>
+    <t>(508) 753-2489</t>
+  </si>
+  <si>
+    <t>100 Martin Luther King Jr Blvd #500, Worcester, MA 01608</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Gregory+Livanos,+DDS/data=!4m7!3m6!1s0x89e4066658b3822d:0x64401e0c6404cd25!8m2!3d42.2668976!4d-71.79662!16s%2Fg%2F1tj8bfkn!19sChIJLYKzWGYG5IkRJc0EZAweQGQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:23:57.122Z</t>
+  </si>
+  <si>
+    <t>Worcester Denture Care Services</t>
+  </si>
+  <si>
+    <t>(508) 939-5257</t>
+  </si>
+  <si>
+    <t>Denture care center</t>
+  </si>
+  <si>
+    <t>652 Park Ave, Worcester, MA 01603</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Sunday7 AM–9 PM; Monday6:30 AM–11 PM; Tuesday6:30 AM–11 PM; Wednesday6:30 AM–11 PM; Thursday6:30 AM–11 PM; Friday6:30 AM–11 PM; SaturdayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Worcester+Denture+Care+Services/data=!4m7!3m6!1s0x89e4059d321aa3af:0xf3ba1cce445d904c!8m2!3d42.2458175!4d-71.835615!16s%2Fg%2F11rwk_181z!19sChIJr6MaMp0F5IkRTJBdRM4cuvM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:24:16.037Z</t>
+  </si>
+  <si>
+    <t>Urgent Dental Link</t>
+  </si>
+  <si>
+    <t>(508) 975-2466</t>
+  </si>
+  <si>
+    <t>88 Prescott St, Worcester, MA 01605</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Urgent+Dental+Link/data=!4m7!3m6!1s0x89e407520372af19:0x9279b4a4b77dede!8m2!3d42.2769645!4d-71.7992797!16s%2Fg%2F11zz76rmm1!19sChIJGa9yA1IH5IkR3t53S0qbJwk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:24:38.190Z</t>
+  </si>
+  <si>
+    <t>Urgent Dental Network</t>
+  </si>
+  <si>
+    <t>(508) 351-0134</t>
+  </si>
+  <si>
+    <t>6 Winter St, Worcester, MA 01604</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Urgent+Dental+Network/data=!4m7!3m6!1s0x89e407c7273c1e85:0xed4303d2dbe7f024!8m2!3d42.2586606!4d-71.7974626!16s%2Fg%2F11p1jncy07!19sChIJhR48J8cH5IkRJPDn29IDQ-0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:24:40.517Z</t>
+  </si>
+  <si>
+    <t>Robert D Babigian Dmd</t>
+  </si>
+  <si>
+    <t>(508) 791-7007</t>
+  </si>
+  <si>
+    <t>111 Elm St Ste 101, Worcester, MA 01609</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Robert+D+Babigian+Dmd/data=!4m7!3m6!1s0x89e40666e79bd74f:0x1a7bcd93de98f4d6!8m2!3d42.2662131!4d-71.8136155!16s%2Fg%2F1tcx2j_w!19sChIJT9eb52YG5IkR1vSY3pPNexo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:24:51.033Z</t>
+  </si>
+  <si>
+    <t>SmileBridge Dental Care</t>
+  </si>
+  <si>
+    <t>(833) 546-3592</t>
+  </si>
+  <si>
+    <t>440 Main St, Worcester, MA 01608</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/SmileBridge+Dental+Care/data=!4m7!3m6!1s0x89e407409a40f31b:0x2dfc7777d03fdbb5!8m2!3d42.2633111!4d-71.8026651!16s%2Fg%2F11n9bc661_!19sChIJG_NAmkAH5IkRtds_0Hd3_C0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:25:04.221Z</t>
+  </si>
+  <si>
+    <t>Savas Athan DDS</t>
+  </si>
+  <si>
+    <t>(508) 798-4800</t>
+  </si>
+  <si>
+    <t>255 Park Ave #1103, Worcester, MA 01609</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Savas+Athan+DDS/data=!4m7!3m6!1s0x89e4068c29f8f5b5:0x560dcbebaf087b03!8m2!3d42.2649492!4d-71.8185051!16s%2Fg%2F1ts_7mhv!19sChIJtfX4KYwG5IkRA3sIr-vLDVY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:25:51.736Z</t>
+  </si>
+  <si>
+    <t>Dr. Lisa A. Antonelli, DMD</t>
+  </si>
+  <si>
+    <t>(508) 753-1911</t>
+  </si>
+  <si>
+    <t>330 Plantation St, Worcester, MA 01604</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Lisa+A.+Antonelli,+DMD/data=!4m7!3m6!1s0x89e406258e8b013b:0xc8c47c8d62fe73a6!8m2!3d42.2712003!4d-71.769956!16s%2Fg%2F1tdwr33_!19sChIJOwGLjiUG5IkRpnP-Yo18xMg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:25:54.157Z</t>
+  </si>
+  <si>
+    <t>Rafla Marta O DDS</t>
+  </si>
+  <si>
+    <t>(508) 363-4300</t>
+  </si>
+  <si>
+    <t>65 Elm St, Worcester, MA 01609</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Rafla+Marta+O+DDS/data=!4m7!3m6!1s0x89e40661cc4ef093:0x86006eee2e8d0590!8m2!3d42.265716!4d-71.8086959!16s%2Fg%2F1td4qqqc!19sChIJk_BOzGEG5IkRkAWNLu5uAIY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:25:56.674Z</t>
+  </si>
+  <si>
+    <t>Carl Cohen PC</t>
+  </si>
+  <si>
+    <t>(508) 754-6566</t>
+  </si>
+  <si>
+    <t>255 Park Ave #405, Worcester, MA 01609</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Carl+Cohen+PC/data=!4m7!3m6!1s0x89e4068c29f8f5b5:0x6bf4f02d27c1e8f!8m2!3d42.2649492!4d-71.8185051!16s%2Fg%2F1wl4rmc6!19sChIJtfX4KYwG5IkRjx580gJPvwY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:25:58.686Z</t>
+  </si>
+  <si>
+    <t>Dr. Kevin Guze</t>
+  </si>
+  <si>
+    <t>(508) 752-1302</t>
+  </si>
+  <si>
+    <t>111 Elm St Ste 203, Worcester, MA 01609</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Kevin+Guze/data=!4m7!3m6!1s0x89e4068ba4e43251:0xee6f484cbdef45e3!8m2!3d42.2662131!4d-71.8136155!16s%2Fg%2F11p07b3f8_!19sChIJUTLkpIsG5IkR40XvvUxIb-4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:26:00.712Z</t>
+  </si>
+  <si>
+    <t>Robert A Desautels, DDS</t>
+  </si>
+  <si>
+    <t>(339) 240-6719</t>
+  </si>
+  <si>
+    <t>34 Marsden St, Springfield, MA 01109</t>
+  </si>
+  <si>
+    <t>Springfield</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Robert+A+Desautels,+DDS/data=!4m7!3m6!1s0x89e6e7f1fab76ff3:0xd9ae755d1cada860!8m2!3d42.127081!4d-72.5377247!16s%2Fg%2F1thmm072!19sChIJ82-3-vHn5okRYKitHF11rtk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:27:19.936Z</t>
+  </si>
+  <si>
+    <t>mnko</t>
+  </si>
+  <si>
+    <t>(413) 239-0006</t>
+  </si>
+  <si>
+    <t>661 Front St Ste B, Chicopee, MA 01013</t>
+  </si>
+  <si>
+    <t>Chicopee</t>
+  </si>
+  <si>
+    <t>3.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/mnko/data=!4m7!3m6!1s0x89e6ddf4ca24294b:0xa0cae99ff1998e30!8m2!3d42.1482996!4d-72.591898!16s%2Fg%2F11fx7xmhsb!19sChIJSykkyvTd5okRMI6Z8Z_pyqA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:27:30.767Z</t>
+  </si>
+  <si>
+    <t>Dr. Chandra Mohan Manish, DMD.</t>
+  </si>
+  <si>
+    <t>(413) 796-4700</t>
+  </si>
+  <si>
+    <t>800 Boston Rd, Springfield, MA 01119</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Chandra+Mohan+Manish,+DMD./data=!4m7!3m6!1s0x89e6c2ab6c5c50fd:0x1258a878816db26!8m2!3d42.1401755!4d-72.5196049!16s%2Fg%2F1vxvjwvl!19sChIJ_VBcbKvC5okRJtsWiIeKJQE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:27:56.760Z</t>
+  </si>
+  <si>
+    <t>Christopher Donohue DMD</t>
+  </si>
+  <si>
+    <t>(413) 737-7912</t>
+  </si>
+  <si>
+    <t>624 Belmont Ave, Springfield, MA 01108</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Christopher+Donohue+DMD/data=!4m7!3m6!1s0x89e6e6434537da35:0xbab702231b3a6216!8m2!3d42.0855029!4d-72.5551585!16s%2Fg%2F1w0j0mnc!19sChIJNdo3RUPm5okRFmI6GyMCt7o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:28:03.858Z</t>
+  </si>
+  <si>
+    <t>West Springfield Family Dental</t>
+  </si>
+  <si>
+    <t>(413) 310-3017</t>
+  </si>
+  <si>
+    <t>1096 Memorial Ave, West Springfield, MA 01089</t>
+  </si>
+  <si>
+    <t>West Springfield</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/West+Springfield+Family+Dental/data=!4m7!3m6!1s0x89e6e134cf3fbccb:0x8e8d81480406ac54!8m2!3d42.0942132!4d-72.6157008!16s%2Fg%2F11b7hm1v9c!19sChIJy7w_zzTh5okRVKwGBEiBjY4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:28:06.104Z</t>
+  </si>
+  <si>
+    <t>Gentle Smiles</t>
+  </si>
+  <si>
+    <t>(413) 739-4500</t>
+  </si>
+  <si>
+    <t>1410 Carew St, Springfield, MA 01104</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Gentle+Smiles/data=!4m7!3m6!1s0x89e6e77f693aef71:0x75696d1380a7fd01!8m2!3d42.137742!4d-72.5693882!16s%2Fg%2F1vzv4ph3!19sChIJce86aX_n5okRAf2ngBNtaXU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:28:40.693Z</t>
+  </si>
+  <si>
+    <t>Dr. Anthony E. Breglio, DMD</t>
+  </si>
+  <si>
+    <t>(413) 734-5522</t>
+  </si>
+  <si>
+    <t>167 Maple St #2, Springfield, MA 01105</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Anthony+E.+Breglio,+DMD/data=!4m7!3m6!1s0x89e6e6fca51c97e3:0x749c4bb2f53e928e!8m2!3d42.099893!4d-72.578729!16s%2Fg%2F1tf5lpb3!19sChIJ45ccpfzm5okRjpI-9bJLnHQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:28:44.624Z</t>
+  </si>
+  <si>
+    <t>Dr. Saboori Sobti</t>
+  </si>
+  <si>
+    <t>(413) 507-0115</t>
+  </si>
+  <si>
+    <t>1795 Main St Ste 212, Springfield, MA 01103</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Saboori+Sobti/data=!4m7!3m6!1s0x89e6e6df3f74b5d7:0xa17becd1a57c2bfa!8m2!3d42.1056369!4d-72.5960998!16s%2Fg%2F11qgb7mlmk!19sChIJ17V0P9_m5okR-it8pdHse6E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:28:48.843Z</t>
+  </si>
+  <si>
+    <t>Pediatric Dentist Offering Comprehensive Dental Care</t>
+  </si>
+  <si>
+    <t>(413) 737-6906</t>
+  </si>
+  <si>
+    <t>46 Daggett Dr #1c, West Springfield, MA 01089</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pediatric+Dentist+Offering+Comprehensive+Dental+Care/data=!4m7!3m6!1s0x89e6e0b7b4332437:0x5b06992433f22071!8m2!3d42.1318523!4d-72.6242971!16s%2Fg%2F11ddyhzz7w!19sChIJNyQztLfg5okRcSDyMySZBls?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:29:03.236Z</t>
+  </si>
+  <si>
+    <t>Dr. Robert L. Matthews, DMD</t>
+  </si>
+  <si>
+    <t>(413) 737-2200</t>
+  </si>
+  <si>
+    <t>232 Park St, West Springfield, MA 01089</t>
+  </si>
+  <si>
+    <t>2.6</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Robert+L.+Matthews,+DMD/data=!4m7!3m6!1s0x89e6e12ef3dac4f5:0x5e759d8f0cadb457!8m2!3d42.1043369!4d-72.6229192!16s%2Fg%2F1tfts380!19sChIJ9cTa8y7h5okRV7StDI-ddV4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:29:08.755Z</t>
+  </si>
+  <si>
+    <t>Nghiem Anne T DDS</t>
+  </si>
+  <si>
+    <t>(413) 787-7079</t>
+  </si>
+  <si>
+    <t>200 Birnie Ave, Springfield, MA 01107</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Nghiem+Anne+T+DDS/data=!4m7!3m6!1s0x89e6e72df2876e1d:0x9def9d8e3e6a92f1!8m2!3d42.11818!4d-72.610501!16s%2Fg%2F1tx4qcqq!19sChIJHW6H8i3n5okR8ZJqPo6d750?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:29:11.462Z</t>
+  </si>
+  <si>
+    <t>Dental Assistance Premier</t>
+  </si>
+  <si>
+    <t>(239) 842-2769</t>
+  </si>
+  <si>
+    <t>15 Hampden St, Springfield, MA 01103</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Assistance+Premier/data=!4m7!3m6!1s0x89e6e7607f06febd:0x479845e44064fb0!8m2!3d42.10374!4d-72.5943398!16s%2Fg%2F11y3hxxtwb!19sChIJvf4Gf2Dn5okRsE8GRF6EeQQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:29:58.327Z</t>
+  </si>
+  <si>
+    <t>Dental Service Corporation Blue Cross</t>
+  </si>
+  <si>
+    <t>(413) 781-7320</t>
+  </si>
+  <si>
+    <t>77 Boylston St, Springfield, MA 01104</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Service+Corporation+Blue+Cross/data=!4m7!3m6!1s0x89e6e6d88c9635e5:0xf05893efd889b66!8m2!3d42.106362!4d-72.5996252!16s%2Fg%2F1263r6wpw!19sChIJ5TWWjNjm5okRZpuI_T6JBQ8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:30:19.613Z</t>
+  </si>
+  <si>
+    <t>Courtyard Dental.</t>
+  </si>
+  <si>
+    <t>(617) 864-1600</t>
+  </si>
+  <si>
+    <t>842 Massachusetts Ave, Cambridge, MA 02139</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Courtyard+Dental./data=!4m7!3m6!1s0x89e37750fa7abe5f:0x498bc8827d858d23!8m2!3d42.3677409!4d-71.1069797!16s%2Fg%2F1tfyfl6b!19sChIJX756-lB344kRI42FfYLIi0k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:31:04.684Z</t>
+  </si>
+  <si>
+    <t>Alvarez Dental Group</t>
+  </si>
+  <si>
+    <t>(617) 441-0088</t>
+  </si>
+  <si>
+    <t>403 Cambridge St, Cambridge, MA 02141</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Alvarez+Dental+Group/data=!4m7!3m6!1s0x89e370b99ca0ccb1:0x2d761f081f6e08a5!8m2!3d42.3715063!4d-71.0828209!16s%2Fg%2F1tjy2htk!19sChIJscygnLlw44kRpQhuHwgfdi0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:31:10.396Z</t>
+  </si>
+  <si>
+    <t>Malta Dental Clinic</t>
+  </si>
+  <si>
+    <t>(617) 661-1120</t>
+  </si>
+  <si>
+    <t>538 Cambridge St, Cambridge, MA 02141</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Malta+Dental+Clinic/data=!4m7!3m6!1s0x89e370b9fdaafff3:0x38ecc49984cd9e5a!8m2!3d42.3716236!4d-71.0853375!16s%2Fg%2F11c2qtdbpg!19sChIJ8_-q_blw44kRWp7NhJnE7Dg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:31:12.578Z</t>
+  </si>
+  <si>
+    <t>Dr. Aristides Exarchos, DMD</t>
+  </si>
+  <si>
+    <t>(617) 492-6070</t>
+  </si>
+  <si>
+    <t>181 Concord Ave #1, Cambridge, MA 02138</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Aristides+Exarchos,+DMD/data=!4m7!3m6!1s0x89e3776d19a38989:0xa3bb18aab6f1379b!8m2!3d42.3822919!4d-71.1304652!16s%2Fg%2F1vgw9m_6!19sChIJiYmjGW1344kRmzfxtqoYu6M?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:31:14.699Z</t>
+  </si>
+  <si>
+    <t>Alegria Dental Group</t>
+  </si>
+  <si>
+    <t>(617) 868-2545</t>
+  </si>
+  <si>
+    <t>1058 Cambridge St, Cambridge, MA 02139</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Alegria+Dental+Group/data=!4m7!3m6!1s0x89e370b48284abbb:0xf82a563abc095b09!8m2!3d42.3728639!4d-71.0950074!16s%2Fg%2F1tfrhsbw!19sChIJu6uEgrRw44kRCVsJvDpWKvg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:31:17.345Z</t>
+  </si>
+  <si>
+    <t>Dental Office</t>
+  </si>
+  <si>
+    <t>(405) 674-1467</t>
+  </si>
+  <si>
+    <t>Canal St, Boston, MA 02114</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Office/data=!4m7!3m6!1s0x89e3712787612387:0xca458fb88b98387d!8m2!3d42.3643876!4d-71.0602414!16s%2Fg%2F11zzr_851r!19sChIJhyNhhydx44kRfTiYi7iPRco?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:31:20.358Z</t>
+  </si>
+  <si>
+    <t>Tranfaglia Sandra N DMD</t>
+  </si>
+  <si>
+    <t>(844) 833-1796</t>
+  </si>
+  <si>
+    <t>17 Washington St #1, Somerville, MA 02143</t>
+  </si>
+  <si>
+    <t>Sunday6 AM–11 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Tranfaglia+Sandra+N+DMD/data=!4m7!3m6!1s0x89e370cbda7d9cb5:0xcded4a2d5f176483!8m2!3d42.3827417!4d-71.0812547!16s%2Fg%2F1tfkb0dw!19sChIJtZx92stw44kRg2QXXy1K7c0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:31:22.699Z</t>
+  </si>
+  <si>
+    <t>Alpha Dental Somerville</t>
+  </si>
+  <si>
+    <t>(617) 764-1454</t>
+  </si>
+  <si>
+    <t>701 Broadway, Somerville, MA 02144</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Alpha+Dental+Somerville/data=!4m7!3m6!1s0x89e376d87d662019:0xd37a7c33f0093ac8!8m2!3d42.4000198!4d-71.1121261!16s%2Fg%2F12lrg1q_y!19sChIJGSBmfdh244kRyDoJ8DN8etM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:31:24.934Z</t>
+  </si>
+  <si>
+    <t>Bright Dental</t>
+  </si>
+  <si>
+    <t>(617) 491-2829</t>
+  </si>
+  <si>
+    <t>435 Washington St #97b, Somerville, MA 02143</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bright+Dental/data=!4m7!3m6!1s0x89e3774846faaaab:0x98acd2f2078cd061!8m2!3d42.3783068!4d-71.107205!16s%2Fg%2F11j03bp7tx!19sChIJq6r6Rkh344kRYdCMB_LSrJg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:31:39.138Z</t>
+  </si>
+  <si>
+    <t>Brown Richard S Dr</t>
+  </si>
+  <si>
+    <t>(617) 864-2577</t>
+  </si>
+  <si>
+    <t>14 Concord Ave APT 203, Cambridge, MA 02138</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Brown+Richard+S+Dr/data=!4m7!3m6!1s0x89e3776bcea6e5bb:0x4d074c42735be676!8m2!3d42.3785722!4d-71.1244495!16s%2Fg%2F1v9gwgv_!19sChIJu-Wmzmt344kRduZbc0JMB00?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:31:41.175Z</t>
+  </si>
+  <si>
+    <t>Rusnock John T DDS</t>
+  </si>
+  <si>
+    <t>(617) 547-0618</t>
+  </si>
+  <si>
+    <t>1105 Massachusetts Ave APT 1E, Cambridge, MA 02138</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Rusnock+John+T+DDS/data=!4m7!3m6!1s0x89e3775b3807ba0d:0xae97019cfd8fb1ed!8m2!3d42.3707933!4d-71.1133748!16s%2Fg%2F1tdm4r6g!19sChIJDboHOFt344kR7bGP_ZwBl64?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:31:45.432Z</t>
+  </si>
+  <si>
+    <t>Dr. Joseph T. Deprimio, DDS</t>
+  </si>
+  <si>
+    <t>(617) 491-9088</t>
+  </si>
+  <si>
+    <t>121 Charles St, Cambridge, MA 02141</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Joseph+T.+Deprimio,+DDS/data=!4m7!3m6!1s0x89e370bb0f0bade3:0xdc2127d85c8b2c0a!8m2!3d42.3679055!4d-71.0817216!16s%2Fg%2F1tdmwmq0!19sChIJ460LD7tw44kRCiyLXNgnIdw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:31:47.726Z</t>
+  </si>
+  <si>
+    <t>Family Dental New England</t>
+  </si>
+  <si>
+    <t>(866) 228-6188</t>
+  </si>
+  <si>
+    <t>714 Massachusetts Ave, Cambridge, MA 02139</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Family+Dental+New+England/data=!4m7!3m6!1s0x89e377513f0a452d:0xf12fc78bde146c10!8m2!3d42.3658599!4d-71.1050727!16s%2Fg%2F1td8_3rl!19sChIJLUUKP1F344kREGwU3ovHL_E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:31:49.614Z</t>
+  </si>
+  <si>
+    <t>Maurice Zylber</t>
+  </si>
+  <si>
+    <t>(617) 876-7900</t>
+  </si>
+  <si>
+    <t>Cosmetic dentist</t>
+  </si>
+  <si>
+    <t>14 Pleasant St, Cambridge, MA 02139</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Maurice+Zylber/data=!4m7!3m6!1s0x89e37ba1cffd61d5:0x5525f33f915c4e48!8m2!3d42.3655732!4d-71.1061488!16s%2Fg%2F1tfx5xnc!19sChIJ1WH9z6F744kRSE5ckT_zJVU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:31:51.485Z</t>
+  </si>
+  <si>
+    <t>Khang Eugene K DMD</t>
+  </si>
+  <si>
+    <t>(617) 576-5300</t>
+  </si>
+  <si>
+    <t>30 Prospect St, Cambridge, MA 02139</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Khang+Eugene+K+DMD/data=!4m7!3m6!1s0x89e377515e2b6d2f:0xa515df85216b6764!8m2!3d42.3658661!4d-71.1035403!16s%2Fg%2F1264g2_f4!19sChIJL20rXlF344kRZGdrIYXfFaU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:33:01.145Z</t>
+  </si>
+  <si>
+    <t>Dr. David Goldberg</t>
+  </si>
+  <si>
+    <t>(617) 354-3300</t>
+  </si>
+  <si>
+    <t>19 White St, Cambridge, MA 02140</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+David+Goldberg/data=!4m7!3m6!1s0x89e3773d110fffe5:0x9452a2f613d6b51!8m2!3d42.3896076!4d-71.1190891!16s%2Fg%2F11sd2y1ld3!19sChIJ5f8PET1344kRUWs9YS8qRQk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:33:42.621Z</t>
+  </si>
+  <si>
+    <t>PRO Smile Dental</t>
+  </si>
+  <si>
+    <t>(617) 928-8555</t>
+  </si>
+  <si>
+    <t>1986 Massachusetts Ave, Cambridge, MA 02140</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/PRO+Smile+Dental/data=!4m7!3m6!1s0x89e377a2e42354a7:0x758b2a1b58cb7d09!8m2!3d42.3900761!4d-71.1211246!16s%2Fg%2F11lmnf9q2t!19sChIJp1Qj5KJ344kRCX3LWBsqi3U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:33:58.699Z</t>
+  </si>
+  <si>
+    <t>Dr. Alex Callejas, DMD</t>
+  </si>
+  <si>
+    <t>(617) 577-8700</t>
+  </si>
+  <si>
+    <t>1 Kendall Square Bldg 300, STE B3104, Cambridge, MA 02139</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Alex+Callejas,+DMD/data=!4m7!3m6!1s0x89e370ade1cbb413:0x511572b3290266f2!8m2!3d42.3661529!4d-71.0907713!16s%2Fg%2F1td5h3qz!19sChIJE7TL4a1w44kR8mYCKbNyFVE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:34:02.645Z</t>
+  </si>
+  <si>
+    <t>Nature America</t>
+  </si>
+  <si>
+    <t>(617) 588-0044</t>
+  </si>
+  <si>
+    <t>Periodontist</t>
+  </si>
+  <si>
+    <t>25 First St #104, East Cambridge, MA 02141</t>
+  </si>
+  <si>
+    <t>East Cambridge</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Nature+America/data=!4m7!3m6!1s0x89e370bc261e50e5:0x184c2a38e0f005d5!8m2!3d42.3696862!4d-71.0779917!16s%2Fg%2F1tffksrp!19sChIJ5VAeJrxw44kR1QXw4DgqTBg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:34:58.618Z</t>
+  </si>
+  <si>
+    <t>Urgent Dental Center</t>
+  </si>
+  <si>
+    <t>(508) 316-5791</t>
+  </si>
+  <si>
+    <t>1060 Fall River Ave, Seekonk, MA 02771</t>
+  </si>
+  <si>
+    <t>Seekonk</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Urgent+Dental+Center/data=!4m7!3m6!1s0x89e45b99e5d2012b:0x3f34f3d0b967e7f6!8m2!3d41.7964547!4d-71.3290564!16s%2Fg%2F11zz0vf8g6!19sChIJKwHS5Zlb5IkR9udnudDzND8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:37:53.046Z</t>
   </si>
 </sst>
 </file>
@@ -742,7 +1561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1415,6 +2234,2056 @@
         <v>116</v>
       </c>
     </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s">
+        <v>120</v>
+      </c>
+      <c r="I17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L17" t="s">
+        <v>121</v>
+      </c>
+      <c r="M17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>125</v>
+      </c>
+      <c r="E18" t="s">
+        <v>102</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s">
+        <v>103</v>
+      </c>
+      <c r="I18" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" t="s">
+        <v>37</v>
+      </c>
+      <c r="K18" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18" t="s">
+        <v>126</v>
+      </c>
+      <c r="M18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E19" t="s">
+        <v>102</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" t="s">
+        <v>37</v>
+      </c>
+      <c r="K19" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" t="s">
+        <v>131</v>
+      </c>
+      <c r="M19" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" t="s">
+        <v>135</v>
+      </c>
+      <c r="E20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s">
+        <v>136</v>
+      </c>
+      <c r="I20" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" t="s">
+        <v>37</v>
+      </c>
+      <c r="K20" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" t="s">
+        <v>137</v>
+      </c>
+      <c r="M20" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>139</v>
+      </c>
+      <c r="B21" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" t="s">
+        <v>141</v>
+      </c>
+      <c r="E21" t="s">
+        <v>102</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s">
+        <v>142</v>
+      </c>
+      <c r="I21" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" t="s">
+        <v>51</v>
+      </c>
+      <c r="K21" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" t="s">
+        <v>143</v>
+      </c>
+      <c r="M21" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>145</v>
+      </c>
+      <c r="B22" t="s">
+        <v>146</v>
+      </c>
+      <c r="C22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" t="s">
+        <v>147</v>
+      </c>
+      <c r="E22" t="s">
+        <v>102</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s">
+        <v>51</v>
+      </c>
+      <c r="I22" t="s">
+        <v>68</v>
+      </c>
+      <c r="J22" t="s">
+        <v>51</v>
+      </c>
+      <c r="K22" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" t="s">
+        <v>148</v>
+      </c>
+      <c r="M22" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>150</v>
+      </c>
+      <c r="B23" t="s">
+        <v>151</v>
+      </c>
+      <c r="C23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" t="s">
+        <v>152</v>
+      </c>
+      <c r="E23" t="s">
+        <v>102</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" t="s">
+        <v>37</v>
+      </c>
+      <c r="K23" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" t="s">
+        <v>153</v>
+      </c>
+      <c r="M23" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>155</v>
+      </c>
+      <c r="B24" t="s">
+        <v>156</v>
+      </c>
+      <c r="C24" t="s">
+        <v>157</v>
+      </c>
+      <c r="D24" t="s">
+        <v>158</v>
+      </c>
+      <c r="E24" t="s">
+        <v>102</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s">
+        <v>159</v>
+      </c>
+      <c r="I24" t="s">
+        <v>160</v>
+      </c>
+      <c r="J24" t="s">
+        <v>161</v>
+      </c>
+      <c r="K24" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" t="s">
+        <v>162</v>
+      </c>
+      <c r="M24" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>164</v>
+      </c>
+      <c r="B25" t="s">
+        <v>165</v>
+      </c>
+      <c r="C25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" t="s">
+        <v>166</v>
+      </c>
+      <c r="E25" t="s">
+        <v>102</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s">
+        <v>51</v>
+      </c>
+      <c r="I25" t="s">
+        <v>68</v>
+      </c>
+      <c r="J25" t="s">
+        <v>51</v>
+      </c>
+      <c r="K25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" t="s">
+        <v>167</v>
+      </c>
+      <c r="M25" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>169</v>
+      </c>
+      <c r="B26" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" t="s">
+        <v>171</v>
+      </c>
+      <c r="E26" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" t="s">
+        <v>51</v>
+      </c>
+      <c r="K26" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" t="s">
+        <v>172</v>
+      </c>
+      <c r="M26" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>174</v>
+      </c>
+      <c r="B27" t="s">
+        <v>175</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" t="s">
+        <v>176</v>
+      </c>
+      <c r="E27" t="s">
+        <v>102</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" t="s">
+        <v>37</v>
+      </c>
+      <c r="K27" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" t="s">
+        <v>177</v>
+      </c>
+      <c r="M27" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>179</v>
+      </c>
+      <c r="B28" t="s">
+        <v>180</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" t="s">
+        <v>181</v>
+      </c>
+      <c r="E28" t="s">
+        <v>102</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s">
+        <v>20</v>
+      </c>
+      <c r="I28" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" t="s">
+        <v>37</v>
+      </c>
+      <c r="K28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" t="s">
+        <v>182</v>
+      </c>
+      <c r="M28" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>184</v>
+      </c>
+      <c r="B29" t="s">
+        <v>185</v>
+      </c>
+      <c r="C29" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" t="s">
+        <v>186</v>
+      </c>
+      <c r="E29" t="s">
+        <v>102</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s">
+        <v>51</v>
+      </c>
+      <c r="I29" t="s">
+        <v>187</v>
+      </c>
+      <c r="J29" t="s">
+        <v>51</v>
+      </c>
+      <c r="K29" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" t="s">
+        <v>188</v>
+      </c>
+      <c r="M29" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>190</v>
+      </c>
+      <c r="B30" t="s">
+        <v>191</v>
+      </c>
+      <c r="C30" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" t="s">
+        <v>192</v>
+      </c>
+      <c r="E30" t="s">
+        <v>102</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s">
+        <v>51</v>
+      </c>
+      <c r="I30" t="s">
+        <v>86</v>
+      </c>
+      <c r="J30" t="s">
+        <v>51</v>
+      </c>
+      <c r="K30" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" t="s">
+        <v>193</v>
+      </c>
+      <c r="M30" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>195</v>
+      </c>
+      <c r="B31" t="s">
+        <v>196</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" t="s">
+        <v>197</v>
+      </c>
+      <c r="E31" t="s">
+        <v>102</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s">
+        <v>20</v>
+      </c>
+      <c r="I31" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" t="s">
+        <v>51</v>
+      </c>
+      <c r="K31" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" t="s">
+        <v>198</v>
+      </c>
+      <c r="M31" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>200</v>
+      </c>
+      <c r="B32" t="s">
+        <v>201</v>
+      </c>
+      <c r="C32" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32" t="s">
+        <v>202</v>
+      </c>
+      <c r="E32" t="s">
+        <v>102</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s">
+        <v>51</v>
+      </c>
+      <c r="I32" t="s">
+        <v>203</v>
+      </c>
+      <c r="J32" t="s">
+        <v>51</v>
+      </c>
+      <c r="K32" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" t="s">
+        <v>204</v>
+      </c>
+      <c r="M32" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>206</v>
+      </c>
+      <c r="B33" t="s">
+        <v>207</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" t="s">
+        <v>208</v>
+      </c>
+      <c r="E33" t="s">
+        <v>102</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s">
+        <v>51</v>
+      </c>
+      <c r="I33" t="s">
+        <v>68</v>
+      </c>
+      <c r="J33" t="s">
+        <v>51</v>
+      </c>
+      <c r="K33" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" t="s">
+        <v>209</v>
+      </c>
+      <c r="M33" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>211</v>
+      </c>
+      <c r="B34" t="s">
+        <v>212</v>
+      </c>
+      <c r="C34" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" t="s">
+        <v>213</v>
+      </c>
+      <c r="E34" t="s">
+        <v>214</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s">
+        <v>20</v>
+      </c>
+      <c r="I34" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" t="s">
+        <v>22</v>
+      </c>
+      <c r="K34" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" t="s">
+        <v>215</v>
+      </c>
+      <c r="M34" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>217</v>
+      </c>
+      <c r="B35" t="s">
+        <v>218</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" t="s">
+        <v>219</v>
+      </c>
+      <c r="E35" t="s">
+        <v>220</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s">
+        <v>221</v>
+      </c>
+      <c r="I35" t="s">
+        <v>21</v>
+      </c>
+      <c r="J35" t="s">
+        <v>22</v>
+      </c>
+      <c r="K35" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" t="s">
+        <v>222</v>
+      </c>
+      <c r="M35" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>224</v>
+      </c>
+      <c r="B36" t="s">
+        <v>225</v>
+      </c>
+      <c r="C36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" t="s">
+        <v>226</v>
+      </c>
+      <c r="E36" t="s">
+        <v>214</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s">
+        <v>94</v>
+      </c>
+      <c r="I36" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s">
+        <v>22</v>
+      </c>
+      <c r="K36" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" t="s">
+        <v>227</v>
+      </c>
+      <c r="M36" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>229</v>
+      </c>
+      <c r="B37" t="s">
+        <v>230</v>
+      </c>
+      <c r="C37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" t="s">
+        <v>231</v>
+      </c>
+      <c r="E37" t="s">
+        <v>214</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" t="s">
+        <v>103</v>
+      </c>
+      <c r="I37" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s">
+        <v>37</v>
+      </c>
+      <c r="K37" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" t="s">
+        <v>232</v>
+      </c>
+      <c r="M37" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>234</v>
+      </c>
+      <c r="B38" t="s">
+        <v>235</v>
+      </c>
+      <c r="C38" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" t="s">
+        <v>236</v>
+      </c>
+      <c r="E38" t="s">
+        <v>237</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" t="s">
+        <v>238</v>
+      </c>
+      <c r="I38" t="s">
+        <v>21</v>
+      </c>
+      <c r="J38" t="s">
+        <v>37</v>
+      </c>
+      <c r="K38" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" t="s">
+        <v>239</v>
+      </c>
+      <c r="M38" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>241</v>
+      </c>
+      <c r="B39" t="s">
+        <v>242</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>243</v>
+      </c>
+      <c r="E39" t="s">
+        <v>214</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" t="s">
+        <v>94</v>
+      </c>
+      <c r="I39" t="s">
+        <v>21</v>
+      </c>
+      <c r="J39" t="s">
+        <v>37</v>
+      </c>
+      <c r="K39" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" t="s">
+        <v>244</v>
+      </c>
+      <c r="M39" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>246</v>
+      </c>
+      <c r="B40" t="s">
+        <v>247</v>
+      </c>
+      <c r="C40" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" t="s">
+        <v>248</v>
+      </c>
+      <c r="E40" t="s">
+        <v>214</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" t="s">
+        <v>249</v>
+      </c>
+      <c r="I40" t="s">
+        <v>21</v>
+      </c>
+      <c r="J40" t="s">
+        <v>37</v>
+      </c>
+      <c r="K40" t="s">
+        <v>23</v>
+      </c>
+      <c r="L40" t="s">
+        <v>250</v>
+      </c>
+      <c r="M40" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>252</v>
+      </c>
+      <c r="B41" t="s">
+        <v>253</v>
+      </c>
+      <c r="C41" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" t="s">
+        <v>254</v>
+      </c>
+      <c r="E41" t="s">
+        <v>214</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" t="s">
+        <v>51</v>
+      </c>
+      <c r="I41" t="s">
+        <v>68</v>
+      </c>
+      <c r="J41" t="s">
+        <v>37</v>
+      </c>
+      <c r="K41" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" t="s">
+        <v>255</v>
+      </c>
+      <c r="M41" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>257</v>
+      </c>
+      <c r="B42" t="s">
+        <v>258</v>
+      </c>
+      <c r="C42" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" t="s">
+        <v>259</v>
+      </c>
+      <c r="E42" t="s">
+        <v>237</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" t="s">
+        <v>51</v>
+      </c>
+      <c r="I42" t="s">
+        <v>68</v>
+      </c>
+      <c r="J42" t="s">
+        <v>51</v>
+      </c>
+      <c r="K42" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" t="s">
+        <v>260</v>
+      </c>
+      <c r="M42" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>262</v>
+      </c>
+      <c r="B43" t="s">
+        <v>263</v>
+      </c>
+      <c r="C43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" t="s">
+        <v>264</v>
+      </c>
+      <c r="E43" t="s">
+        <v>237</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43" t="s">
+        <v>265</v>
+      </c>
+      <c r="I43" t="s">
+        <v>21</v>
+      </c>
+      <c r="J43" t="s">
+        <v>37</v>
+      </c>
+      <c r="K43" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" t="s">
+        <v>266</v>
+      </c>
+      <c r="M43" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>268</v>
+      </c>
+      <c r="B44" t="s">
+        <v>269</v>
+      </c>
+      <c r="C44" t="s">
+        <v>48</v>
+      </c>
+      <c r="D44" t="s">
+        <v>270</v>
+      </c>
+      <c r="E44" t="s">
+        <v>214</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" t="s">
+        <v>51</v>
+      </c>
+      <c r="I44" t="s">
+        <v>68</v>
+      </c>
+      <c r="J44" t="s">
+        <v>51</v>
+      </c>
+      <c r="K44" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" t="s">
+        <v>271</v>
+      </c>
+      <c r="M44" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>273</v>
+      </c>
+      <c r="B45" t="s">
+        <v>274</v>
+      </c>
+      <c r="C45" t="s">
+        <v>56</v>
+      </c>
+      <c r="D45" t="s">
+        <v>275</v>
+      </c>
+      <c r="E45" t="s">
+        <v>214</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" t="s">
+        <v>20</v>
+      </c>
+      <c r="I45" t="s">
+        <v>21</v>
+      </c>
+      <c r="J45" t="s">
+        <v>51</v>
+      </c>
+      <c r="K45" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" t="s">
+        <v>276</v>
+      </c>
+      <c r="M45" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>278</v>
+      </c>
+      <c r="B46" t="s">
+        <v>279</v>
+      </c>
+      <c r="C46" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" t="s">
+        <v>280</v>
+      </c>
+      <c r="E46" t="s">
+        <v>214</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" t="s">
+        <v>51</v>
+      </c>
+      <c r="I46" t="s">
+        <v>68</v>
+      </c>
+      <c r="J46" t="s">
+        <v>51</v>
+      </c>
+      <c r="K46" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" t="s">
+        <v>281</v>
+      </c>
+      <c r="M46" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>283</v>
+      </c>
+      <c r="B47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C47" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" t="s">
+        <v>285</v>
+      </c>
+      <c r="E47" t="s">
+        <v>74</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" t="s">
+        <v>103</v>
+      </c>
+      <c r="I47" t="s">
+        <v>21</v>
+      </c>
+      <c r="J47" t="s">
+        <v>37</v>
+      </c>
+      <c r="K47" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" t="s">
+        <v>286</v>
+      </c>
+      <c r="M47" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>288</v>
+      </c>
+      <c r="B48" t="s">
+        <v>289</v>
+      </c>
+      <c r="C48" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" t="s">
+        <v>290</v>
+      </c>
+      <c r="E48" t="s">
+        <v>74</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" t="s">
+        <v>159</v>
+      </c>
+      <c r="I48" t="s">
+        <v>21</v>
+      </c>
+      <c r="J48" t="s">
+        <v>37</v>
+      </c>
+      <c r="K48" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" t="s">
+        <v>291</v>
+      </c>
+      <c r="M48" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>293</v>
+      </c>
+      <c r="B49" t="s">
+        <v>294</v>
+      </c>
+      <c r="C49" t="s">
+        <v>28</v>
+      </c>
+      <c r="D49" t="s">
+        <v>295</v>
+      </c>
+      <c r="E49" t="s">
+        <v>74</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" t="s">
+        <v>51</v>
+      </c>
+      <c r="I49" t="s">
+        <v>68</v>
+      </c>
+      <c r="J49" t="s">
+        <v>51</v>
+      </c>
+      <c r="K49" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" t="s">
+        <v>296</v>
+      </c>
+      <c r="M49" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>298</v>
+      </c>
+      <c r="B50" t="s">
+        <v>299</v>
+      </c>
+      <c r="C50" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" t="s">
+        <v>300</v>
+      </c>
+      <c r="E50" t="s">
+        <v>74</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50" t="s">
+        <v>36</v>
+      </c>
+      <c r="I50" t="s">
+        <v>21</v>
+      </c>
+      <c r="J50" t="s">
+        <v>37</v>
+      </c>
+      <c r="K50" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" t="s">
+        <v>301</v>
+      </c>
+      <c r="M50" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>303</v>
+      </c>
+      <c r="B51" t="s">
+        <v>304</v>
+      </c>
+      <c r="C51" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" t="s">
+        <v>305</v>
+      </c>
+      <c r="E51" t="s">
+        <v>74</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51" t="s">
+        <v>120</v>
+      </c>
+      <c r="I51" t="s">
+        <v>21</v>
+      </c>
+      <c r="J51" t="s">
+        <v>37</v>
+      </c>
+      <c r="K51" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" t="s">
+        <v>306</v>
+      </c>
+      <c r="M51" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>308</v>
+      </c>
+      <c r="B52" t="s">
+        <v>309</v>
+      </c>
+      <c r="C52" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" t="s">
+        <v>310</v>
+      </c>
+      <c r="E52" t="s">
+        <v>17</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>19</v>
+      </c>
+      <c r="H52" t="s">
+        <v>51</v>
+      </c>
+      <c r="I52" t="s">
+        <v>68</v>
+      </c>
+      <c r="J52" t="s">
+        <v>22</v>
+      </c>
+      <c r="K52" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" t="s">
+        <v>311</v>
+      </c>
+      <c r="M52" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>313</v>
+      </c>
+      <c r="B53" t="s">
+        <v>314</v>
+      </c>
+      <c r="C53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D53" t="s">
+        <v>315</v>
+      </c>
+      <c r="E53" t="s">
+        <v>93</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" t="s">
+        <v>20</v>
+      </c>
+      <c r="I53" t="s">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s">
+        <v>316</v>
+      </c>
+      <c r="K53" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" t="s">
+        <v>317</v>
+      </c>
+      <c r="M53" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>319</v>
+      </c>
+      <c r="B54" t="s">
+        <v>320</v>
+      </c>
+      <c r="C54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" t="s">
+        <v>321</v>
+      </c>
+      <c r="E54" t="s">
+        <v>93</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" t="s">
+        <v>120</v>
+      </c>
+      <c r="I54" t="s">
+        <v>21</v>
+      </c>
+      <c r="J54" t="s">
+        <v>37</v>
+      </c>
+      <c r="K54" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" t="s">
+        <v>322</v>
+      </c>
+      <c r="M54" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>324</v>
+      </c>
+      <c r="B55" t="s">
+        <v>325</v>
+      </c>
+      <c r="C55" t="s">
+        <v>28</v>
+      </c>
+      <c r="D55" t="s">
+        <v>326</v>
+      </c>
+      <c r="E55" t="s">
+        <v>93</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55" t="s">
+        <v>20</v>
+      </c>
+      <c r="I55" t="s">
+        <v>21</v>
+      </c>
+      <c r="J55" t="s">
+        <v>37</v>
+      </c>
+      <c r="K55" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" t="s">
+        <v>327</v>
+      </c>
+      <c r="M55" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>329</v>
+      </c>
+      <c r="B56" t="s">
+        <v>330</v>
+      </c>
+      <c r="C56" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" t="s">
+        <v>331</v>
+      </c>
+      <c r="E56" t="s">
+        <v>74</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" t="s">
+        <v>20</v>
+      </c>
+      <c r="I56" t="s">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s">
+        <v>51</v>
+      </c>
+      <c r="K56" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" t="s">
+        <v>332</v>
+      </c>
+      <c r="M56" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>334</v>
+      </c>
+      <c r="B57" t="s">
+        <v>335</v>
+      </c>
+      <c r="C57" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" t="s">
+        <v>336</v>
+      </c>
+      <c r="E57" t="s">
+        <v>74</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" t="s">
+        <v>20</v>
+      </c>
+      <c r="I57" t="s">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s">
+        <v>51</v>
+      </c>
+      <c r="K57" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" t="s">
+        <v>337</v>
+      </c>
+      <c r="M57" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>339</v>
+      </c>
+      <c r="B58" t="s">
+        <v>340</v>
+      </c>
+      <c r="C58" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" t="s">
+        <v>341</v>
+      </c>
+      <c r="E58" t="s">
+        <v>74</v>
+      </c>
+      <c r="F58" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" t="s">
+        <v>342</v>
+      </c>
+      <c r="I58" t="s">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s">
+        <v>37</v>
+      </c>
+      <c r="K58" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" t="s">
+        <v>343</v>
+      </c>
+      <c r="M58" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>345</v>
+      </c>
+      <c r="B59" t="s">
+        <v>346</v>
+      </c>
+      <c r="C59" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" t="s">
+        <v>347</v>
+      </c>
+      <c r="E59" t="s">
+        <v>74</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" t="s">
+        <v>20</v>
+      </c>
+      <c r="I59" t="s">
+        <v>21</v>
+      </c>
+      <c r="J59" t="s">
+        <v>51</v>
+      </c>
+      <c r="K59" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" t="s">
+        <v>348</v>
+      </c>
+      <c r="M59" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>350</v>
+      </c>
+      <c r="B60" t="s">
+        <v>351</v>
+      </c>
+      <c r="C60" t="s">
+        <v>352</v>
+      </c>
+      <c r="D60" t="s">
+        <v>353</v>
+      </c>
+      <c r="E60" t="s">
+        <v>74</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" t="s">
+        <v>19</v>
+      </c>
+      <c r="H60" t="s">
+        <v>20</v>
+      </c>
+      <c r="I60" t="s">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s">
+        <v>51</v>
+      </c>
+      <c r="K60" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" t="s">
+        <v>354</v>
+      </c>
+      <c r="M60" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>356</v>
+      </c>
+      <c r="B61" t="s">
+        <v>357</v>
+      </c>
+      <c r="C61" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61" t="s">
+        <v>358</v>
+      </c>
+      <c r="E61" t="s">
+        <v>74</v>
+      </c>
+      <c r="F61" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" t="s">
+        <v>19</v>
+      </c>
+      <c r="H61" t="s">
+        <v>20</v>
+      </c>
+      <c r="I61" t="s">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s">
+        <v>37</v>
+      </c>
+      <c r="K61" t="s">
+        <v>23</v>
+      </c>
+      <c r="L61" t="s">
+        <v>359</v>
+      </c>
+      <c r="M61" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>361</v>
+      </c>
+      <c r="B62" t="s">
+        <v>362</v>
+      </c>
+      <c r="C62" t="s">
+        <v>84</v>
+      </c>
+      <c r="D62" t="s">
+        <v>363</v>
+      </c>
+      <c r="E62" t="s">
+        <v>74</v>
+      </c>
+      <c r="F62" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" t="s">
+        <v>51</v>
+      </c>
+      <c r="I62" t="s">
+        <v>364</v>
+      </c>
+      <c r="J62" t="s">
+        <v>51</v>
+      </c>
+      <c r="K62" t="s">
+        <v>23</v>
+      </c>
+      <c r="L62" t="s">
+        <v>365</v>
+      </c>
+      <c r="M62" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>367</v>
+      </c>
+      <c r="B63" t="s">
+        <v>368</v>
+      </c>
+      <c r="C63" t="s">
+        <v>56</v>
+      </c>
+      <c r="D63" t="s">
+        <v>369</v>
+      </c>
+      <c r="E63" t="s">
+        <v>74</v>
+      </c>
+      <c r="F63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" t="s">
+        <v>19</v>
+      </c>
+      <c r="H63" t="s">
+        <v>20</v>
+      </c>
+      <c r="I63" t="s">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s">
+        <v>51</v>
+      </c>
+      <c r="K63" t="s">
+        <v>23</v>
+      </c>
+      <c r="L63" t="s">
+        <v>370</v>
+      </c>
+      <c r="M63" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>372</v>
+      </c>
+      <c r="B64" t="s">
+        <v>373</v>
+      </c>
+      <c r="C64" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" t="s">
+        <v>374</v>
+      </c>
+      <c r="E64" t="s">
+        <v>74</v>
+      </c>
+      <c r="F64" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" t="s">
+        <v>19</v>
+      </c>
+      <c r="H64" t="s">
+        <v>51</v>
+      </c>
+      <c r="I64" t="s">
+        <v>68</v>
+      </c>
+      <c r="J64" t="s">
+        <v>22</v>
+      </c>
+      <c r="K64" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" t="s">
+        <v>375</v>
+      </c>
+      <c r="M64" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>377</v>
+      </c>
+      <c r="B65" t="s">
+        <v>378</v>
+      </c>
+      <c r="C65" t="s">
+        <v>379</v>
+      </c>
+      <c r="D65" t="s">
+        <v>380</v>
+      </c>
+      <c r="E65" t="s">
+        <v>381</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" t="s">
+        <v>19</v>
+      </c>
+      <c r="H65" t="s">
+        <v>51</v>
+      </c>
+      <c r="I65" t="s">
+        <v>68</v>
+      </c>
+      <c r="J65" t="s">
+        <v>51</v>
+      </c>
+      <c r="K65" t="s">
+        <v>23</v>
+      </c>
+      <c r="L65" t="s">
+        <v>382</v>
+      </c>
+      <c r="M65" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>384</v>
+      </c>
+      <c r="B66" t="s">
+        <v>385</v>
+      </c>
+      <c r="C66" t="s">
+        <v>56</v>
+      </c>
+      <c r="D66" t="s">
+        <v>386</v>
+      </c>
+      <c r="E66" t="s">
+        <v>387</v>
+      </c>
+      <c r="F66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" t="s">
+        <v>19</v>
+      </c>
+      <c r="H66" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" t="s">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s">
+        <v>51</v>
+      </c>
+      <c r="K66" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" t="s">
+        <v>388</v>
+      </c>
+      <c r="M66" t="s">
+        <v>389</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
